--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>Updated 2026-05-14. Repo-backed tracker reflects current Stage Shell, render-field, and live-harness evidence.</t>
   </si>
@@ -307,6 +307,63 @@
   </si>
   <si>
     <t>Planned</t>
+  </si>
+  <si>
+    <t>Updated 2026-05-14. Repo-backed tracker reflects current Stage Shell, Browser validation, render-field, and live-harness evidence.</t>
+  </si>
+  <si>
+    <t>Render organization intelligence v1</t>
+  </si>
+  <si>
+    <t>Taste-review active render field after voice pass</t>
+  </si>
+  <si>
+    <t>Use Browser plugin for manual visual QA</t>
+  </si>
+  <si>
+    <t>Render organization intelligence v1 added; Browser-plugin visual QA still needs Cheick taste review.</t>
+  </si>
+  <si>
+    <t>LOG-004</t>
+  </si>
+  <si>
+    <t>Render organization intelligence pass</t>
+  </si>
+  <si>
+    <t>Primary plan display, topology strip, cleaner command rail, and short-viewport collision handling.</t>
+  </si>
+  <si>
+    <t>First Browser screenshot exposed crowding; second pass hid secondary chrome in shallow viewport.</t>
+  </si>
+  <si>
+    <t>Cheick flagged lack of organization intelligence and display quality.</t>
+  </si>
+  <si>
+    <t>Hierarchy has to be legible before live tool use feels magical.</t>
+  </si>
+  <si>
+    <t>Browser-plugin validation catches compact-surface overlap missed by large screenshots.</t>
+  </si>
+  <si>
+    <t>DEC-005</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Manual rendered QA should use the Browser plugin before standalone Playwright fallback.</t>
+  </si>
+  <si>
+    <t>Cheick explicitly requested Browser for testing rendered local UI.</t>
+  </si>
+  <si>
+    <t>Standalone Playwright only; Browser-first visual QA</t>
+  </si>
+  <si>
+    <t>docs/research/runs/2026-05-14-render-organization-intelligence-slice.md</t>
+  </si>
+  <si>
+    <t>Render organization intelligence v1 added; Cheick taste review remains open.</t>
   </si>
 </sst>
 </file>
@@ -944,7 +1001,7 @@
     </row>
     <row r="2">
       <c r="A2" s="22" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="B2" t="str"/>
       <c r="C2" t="str"/>
@@ -1115,7 +1172,7 @@
     </row>
     <row r="15">
       <c r="A15" s="26" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>10</v>
@@ -1148,7 +1205,7 @@
     </row>
     <row r="18">
       <c r="A18" s="26" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>12</v>
@@ -1159,24 +1216,24 @@
     </row>
     <row r="19">
       <c r="A19" s="26" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2204,7 +2261,7 @@
         <v>Screenshots show idle, working, approval, artifact states.</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -2620,6 +2677,38 @@
         <v>39</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C2:C100">
@@ -2808,6 +2897,38 @@
         <v>54</v>
       </c>
       <c r="J5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3256,7 +3377,7 @@
       </c>
       <c r="E8" t="str"/>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">

--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>Updated 2026-05-14. Repo-backed tracker reflects current Stage Shell, render-field, and live-harness evidence.</t>
   </si>
@@ -364,6 +364,147 @@
   </si>
   <si>
     <t>Render organization intelligence v1 added; Cheick taste review remains open.</t>
+  </si>
+  <si>
+    <t>Updated 2026-05-14. Repo-backed tracker now includes cinematic render-system study, StageSceneManifest contract, Browser-first visual QA, and live-harness evidence.</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Cinematic render system Phase 1</t>
+  </si>
+  <si>
+    <t>Codex</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>BS-019</t>
+  </si>
+  <si>
+    <t>Stage Rendering</t>
+  </si>
+  <si>
+    <t>1 Stage Shell v0</t>
+  </si>
+  <si>
+    <t>Create cinematic scene manifest and fluid vector renderer</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>Codex</t>
+  </si>
+  <si>
+    <t>IntentThread compiles to scene manifest; UI renders semantic roles, edges, and liquid field without dashboard feel.</t>
+  </si>
+  <si>
+    <t>stage-core/stage-web typecheck; Browser-plugin screenshot; e2e visual assertions.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>BS-003, BS-008, BS-018</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manifest contract started from video/json-render study; Phase 1 vector field next.</t>
+  </si>
+  <si>
+    <t>LOG-005</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>UX/Research</t>
+  </si>
+  <si>
+    <t>BS-019</t>
+  </si>
+  <si>
+    <t>Study cinematic demo video and json-render prior art</t>
+  </si>
+  <si>
+    <t>Extracted video frames, inspected json-render, and added StageSceneManifest contract.</t>
+  </si>
+  <si>
+    <t>No live aesthetic validation yet; next slice must prove the vector field visually.</t>
+  </si>
+  <si>
+    <t>Cheick supplied target video and called current display not good enough.</t>
+  </si>
+  <si>
+    <t>The target is a cognitive scene system, not prettier cards.</t>
+  </si>
+  <si>
+    <t>Borrow guarded specs and patch streams from json-render, but render scene semantics.</t>
+  </si>
+  <si>
+    <t>docs/research/runs/2026-05-14-cinematic-render-system-study.md</t>
+  </si>
+  <si>
+    <t>Build StageSceneField vector layer and Browser screenshot gate.</t>
+  </si>
+  <si>
+    <t>DEC-006</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>Rendering</t>
+  </si>
+  <si>
+    <t>Blackstage render system will use a guarded scene manifest and patch stream, not arbitrary generated UI or static cards.</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>Cheick + Codex</t>
+  </si>
+  <si>
+    <t>The video target requires cinematic scene semantics while preserving replayability and approval safety.</t>
+  </si>
+  <si>
+    <t>Static CSS cards; arbitrary agent DOM; json-render component tree; Blackstage scene graph.</t>
+  </si>
+  <si>
+    <t>docs/28_cinematic_rendering_system.md</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>Inspired by json-render contracts, adapted for camera, substrate, material, motion, clusters, and edges.</t>
+  </si>
+  <si>
+    <t>Orb-first idle, scene manifest contract, and spatial render field; continue vector-field and taste QA after live sessions.</t>
+  </si>
+  <si>
+    <t>StageSceneManifest moves taste-critical organization into code; Browser-plugin visual QA remains the gate.</t>
   </si>
 </sst>
 </file>
@@ -705,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N19" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N21" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Workstream"/>
@@ -976,7 +1117,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52" hidden="0" customWidth="1"/>
@@ -1001,7 +1142,7 @@
     </row>
     <row r="2">
       <c r="A2" s="22" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B2" t="str"/>
       <c r="C2" t="str"/>
@@ -1035,8 +1176,8 @@
       <c r="A5" s="26" t="str">
         <v>Backlog Tasks</v>
       </c>
-      <c r="B5" s="26">
-        <v>18</v>
+      <c r="B5" s="26" t="str">
+        <v>20</v>
       </c>
       <c r="C5" s="26" t="str">
         <v>Total initial tasks</v>
@@ -1047,16 +1188,16 @@
       <c r="F5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="26">
-        <v>15</v>
+      <c r="G5" s="26" t="str">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <v>Done Tasks</v>
       </c>
-      <c r="B6" s="26">
-        <v>15</v>
+      <c r="B6" s="26" t="str">
+        <v>16</v>
       </c>
       <c r="C6" s="26" t="str">
         <v>Completed items</v>
@@ -1075,8 +1216,8 @@
       <c r="A7" s="26" t="str">
         <v>In Progress Tasks</v>
       </c>
-      <c r="B7" s="26">
-        <v>3</v>
+      <c r="B7" s="26" t="s">
+        <v>118</v>
       </c>
       <c r="C7" s="26" t="str">
         <v>Active work</v>
@@ -1087,16 +1228,16 @@
       <c r="F7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="26">
-        <v>0</v>
+      <c r="G7" s="26" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="str">
         <v>P0 Tasks</v>
       </c>
-      <c r="B8" s="26">
-        <v>13</v>
+      <c r="B8" s="26" t="s">
+        <v>119</v>
       </c>
       <c r="C8" s="26" t="str">
         <v>Critical path</v>
@@ -1171,14 +1312,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="s">
-        <v>98</v>
+      <c r="A15" s="26" t="str">
+        <v>Build StageSceneField vector layer and live voice debug overlay</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>1</v>
+        <v>122</v>
+      </c>
+      <c r="C15" s="26" t="str">
+        <v>In Progress</v>
       </c>
     </row>
     <row r="16">
@@ -1242,7 +1383,7 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="R88fb916a896f4ef7"/>
+  <drawing ns1:id="R88fb916a896f4ef7"/>
 </worksheet>
 </file>
 
@@ -1528,7 +1669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" hidden="0" customWidth="1"/>
@@ -2272,6 +2413,90 @@
       <c r="L19" t="str"/>
       <c r="M19" t="str"/>
       <c r="N19" t="str"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" t="s">
+        <v>133</v>
+      </c>
+      <c r="K20" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" t="s">
+        <v>135</v>
+      </c>
+      <c r="M20" t="s">
+        <v>136</v>
+      </c>
+      <c r="N20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BS-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Stage Frontend</v>
+      </c>
+      <c r="C21" t="str">
+        <v>1 Stage Shell v0</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Browser compact render QA and orb voice entry</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Done</v>
+      </c>
+      <c r="F21" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Codex</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Browser in-app compact viewport keeps active stage regions separated and live voice/debug controls reachable.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Browser plugin geometry check reports zero overlaps and visible Speak/Export controls.</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K21" t="str">
+        <v>BS-018, BS-019</v>
+      </c>
+      <c r="L21" t="str"/>
+      <c r="M21" t="str"/>
+      <c r="N21" t="str">
+        <v>Logged in 2026-05-15 browser compact render slice.</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
@@ -2300,7 +2525,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R281c859479774d5c"/>
+    <tablePart ns1:id="R281c859479774d5c"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2534,7 +2759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" hidden="0" customWidth="1"/>
@@ -2709,6 +2934,82 @@
         <v>108</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LOG-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>UX/Validation</v>
+      </c>
+      <c r="D7" t="str">
+        <v>BS-020</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Browser compact render and orb entry QA</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Idle orb is demo-free; compact active field keeps intent, plan, evidence, labor, approval, artifact, command, and research zones separated.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Initial compact pass hid command/debug; focused dock then overlapped the document object before the one-row compact fix.</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Cheick explicitly corrected tool choice to Browser plugin.</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Quiet chrome must stay reachable; hidden controls cannot block live testing.</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Browser plugin catches real in-app viewport issues that headless gates can miss.</v>
+      </c>
+      <c r="K7" t="str">
+        <v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Continue StageSceneField vector layer and live voice debug QA.</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C2:C100">
@@ -2717,13 +3018,13 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="Rdb356ef7547d4528"/>
+    <tablePart ns1:id="Rdb356ef7547d4528"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" hidden="0" customWidth="1"/>
@@ -2932,6 +3233,76 @@
         <v>48</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DEC-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Rendering</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Compact active sessions must keep voice and debug entrypoints reachable instead of hiding them completely.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Accepted</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Cheick + Codex</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Live testing depends on visible Speak and debug export controls even when the field is intentionally quiet.</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Hide all chrome; always show full panels; compact one-row command and trace controls</v>
+      </c>
+      <c r="I8" t="str">
+        <v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</v>
+      </c>
+      <c r="J8" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Browser plugin geometry check is the acceptance gate for compact active sessions.</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2:C100">
@@ -2943,13 +3314,13 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="Rb9393f6f1d2545c7"/>
+    <tablePart ns1:id="Rb9393f6f1d2545c7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
@@ -3020,7 +3391,7 @@
         <v>Kills category thesis.</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="H2" t="str">
         <v>Cheick</v>
@@ -3185,7 +3556,7 @@
         <v>Product becomes undifferentiated.</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="H7" t="str">
         <v>GPT-5.5 Pro</v>
@@ -3217,7 +3588,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R5cf31a07ae2a4736"/>
+    <tablePart ns1:id="R5cf31a07ae2a4736"/>
   </tableParts>
 </worksheet>
 </file>

--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -2498,6 +2498,150 @@
         <v>Logged in 2026-05-15 browser compact render slice.</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BS-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Stage Rendering</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1 Stage Shell v0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Make render field the goal center: semantic stage coordinates and focal floor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Active field uses scene coordinates, a focal floor/horizon, hidden QA deep links, and Browser evidence without visible demo buttons.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Browser desktop/mobile visual QA; typecheck/lint/build/test</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>BS-019, BS-020</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Next: central approval ritual and geometric agent labor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BS-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stage Rendering</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1 Stage Shell v0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Turn approval and agent labor into central cinematic scene objects</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pending approvals dim the field and become central ritual objects; agent labor can expand from geometry into audit feed.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Browser visual QA plus e2e scene-manifest assertions</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>BS-021</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Reference video frames show approval/action and labor geometry as the next gap.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3010,6 +3154,130 @@
         <v>Continue StageSceneField vector layer and live voice debug QA.</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LOG-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UX/Research</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BS-021</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Frame-by-frame render field reference analysis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Extracted all 192 frames and translated the video into stage, focal, approval, and labor requirements.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Confirmed prior UI still leaned too much toward cards/dashboard composition.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cheick supplied a second cinematic reference and redirected the goal toward rendering field animation.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>One focal object plus orbiting support reads smarter than many equal panels.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Frame sampling turned taste feedback into concrete renderer requirements.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>docs/research/runs/2026-05-15-render-field-reference-analysis.md</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Build central approval ritual and geometric labor field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LOG-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UX/Build</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BS-021</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Semantic stage-coordinate render pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>StageSceneManifest now drives x/y/depth/scale; StageSceneField draws focal floor and horizon; Browser QA shows no active-field overlaps.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Browser input path exposed clipboard limitations, so hidden scenario/instant QA links were added.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>None beyond Cheick's rendering-first correction.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The field must own organization; CSS grid placement is not enough.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Browser visual checks need deterministic deep links that do not pollute startup UX.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>docs/research/runs/2026-05-15-stage-scene-field-vector-slice.md</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Make approval and labor materialize as central scene states.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C2:C100">
@@ -3301,6 +3569,120 @@
       </c>
       <c r="K8" t="str">
         <v>Browser plugin geometry check is the acceptance gate for compact active sessions.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DEC-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rendering</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The active goal is rendering-first until the field itself feels like organized intelligence.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cheick + Codex</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>The project thesis fails if runtime features work but the surface still reads like a dark dashboard.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Continue backend/runtime first; polish cards; render-field-first goal amendment.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>codex/goals/first_long_run_stage_shell_v0_after_prompt1.md</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Reference video 2 is now a north-star artifact for stage composition and motion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Use hidden deep-link QA parameters for visual scenarios instead of visible demo buttons.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>The startup UX must remain one orb and one instruction while Browser QA still needs deterministic active states.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Visible demo buttons; manual typing only; hidden query controls.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>docs/28_cinematic_rendering_system.md</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Supported query controls: stageScenario, stageIntent, stageInstant, stageDelayMultiplier.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -846,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N21" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N24" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Workstream"/>
@@ -2642,6 +2642,78 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BS-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stage Rendering</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1 Stage Shell v0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Add semantic render zones and flow spine</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>StageSceneManifest emits active zones; StageSceneField renders zone bands/flow; approved desktop scenes keep objects and command dock clear.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Browser desktop geometry QA and targeted e2e overlap gate pass.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BS-021, BS-022</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Browser found approved-scene overlap; anchors and zone grammar were retuned. Next: central approval ritual.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3278,6 +3350,68 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOG-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UX/Build</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BS-023</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Render zone flow and overlap hardening</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Added semantic scene zones, zone-flow spine, retuned anchors, and e2e geometry checks for approved scenes.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Browser desktop QA exposed focal-plan overlap from secondary task/model objects before the retune.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cheick asked to continue systematically toward the reality-interface goal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The field needs a visible grammar, not only better object coordinates.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Browser geometry turns taste feedback into deterministic renderer work.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Make approval and visible labor feel central instead of rail-shaped.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C2:C100">
@@ -3682,6 +3816,63 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>Supported query controls: stageScenario, stageIntent, stageInstant, stageDelayMultiplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rendering</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Render organization belongs in semantic zones plus measured geometry gates, not only CSS placement.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The user must feel the field organizing intelligence before reading individual cards.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Card coordinates only; semantic zones; full physics engine.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>The next renderer target is central approval and labor geometry.</t>
         </is>
       </c>
     </row>

--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -846,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N24" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N25" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Workstream"/>
@@ -1669,1081 +1669,1153 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="52" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="36" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="14" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="28" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="6" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" s="6" t="str">
-        <v>Workstream</v>
-      </c>
-      <c r="C1" s="6" t="str">
-        <v>Phase</v>
-      </c>
-      <c r="D1" s="6" t="str">
-        <v>Task</v>
-      </c>
-      <c r="E1" s="6" t="str">
-        <v>Status</v>
-      </c>
-      <c r="F1" s="6" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G1" s="6" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="H1" s="6" t="str">
-        <v>Acceptance Criteria</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <v>Verification</v>
-      </c>
-      <c r="J1" s="6" t="str">
-        <v>Research Log Required</v>
-      </c>
-      <c r="K1" s="6" t="str">
-        <v>Dependencies</v>
-      </c>
-      <c r="L1" s="6" t="str">
-        <v>PR Link</v>
-      </c>
-      <c r="M1" s="6" t="str">
-        <v>Due Date</v>
-      </c>
-      <c r="N1" s="6" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>BS-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Foundation</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0 Foundation</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Initialize monorepo and workspace commands</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Repo has apps/packages structure and install/dev/build/typecheck commands.</v>
-      </c>
-      <c r="I2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K2" t="str"/>
-      <c r="L2" t="str"/>
-      <c r="M2" t="str"/>
-      <c r="N2" t="str"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BS-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Foundation</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0 Foundation</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Install AGENTS.md and docs into repo root</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Cheick + Codex</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Codex can summarize project mission and active instructions.</v>
-      </c>
-      <c r="I3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K3" t="str">
-        <v>BS-001</v>
-      </c>
-      <c r="L3" t="str"/>
-      <c r="M3" t="str"/>
-      <c r="N3" t="str"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BS-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Core State</v>
-      </c>
-      <c r="C4" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Define IntentThread, StageObject, AgentEvent, ApprovalRequest, Artifact, ResearchEvent types</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Types exported from stage-core and used by app.</v>
-      </c>
-      <c r="I4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K4" t="str">
-        <v>BS-001</v>
-      </c>
-      <c r="L4" t="str"/>
-      <c r="M4" t="str"/>
-      <c r="N4" t="str"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BS-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Stage Frontend</v>
-      </c>
-      <c r="C5" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Build full-screen black StageRoot and PresenceCore</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Idle stage looks cinematic and not like chatbot.</v>
-      </c>
-      <c r="I5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K5" t="str">
-        <v>BS-001</v>
-      </c>
-      <c r="L5" t="str"/>
-      <c r="M5" t="str"/>
-      <c r="N5" t="str"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>BS-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Stage Frontend</v>
-      </c>
-      <c r="C6" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Add text intent submission and transcript display</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H6" t="str">
-        <v>User submits intent and sees it captured as first-class object.</v>
-      </c>
-      <c r="I6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K6" t="str">
-        <v>BS-003, BS-004</v>
-      </c>
-      <c r="L6" t="str"/>
-      <c r="M6" t="str"/>
-      <c r="N6" t="str"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BS-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Core State</v>
-      </c>
-      <c r="C7" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Create intent thread reducer and local persistence</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Threads persist across reload and can be resumed.</v>
-      </c>
-      <c r="I7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K7" t="str">
-        <v>BS-003</v>
-      </c>
-      <c r="L7" t="str"/>
-      <c r="M7" t="str"/>
-      <c r="N7" t="str"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>BS-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Agent Runtime</v>
-      </c>
-      <c r="C8" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Implement simulated agent event stream</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Activity feed streams planned/started/progress/completed/approval_needed events.</v>
-      </c>
-      <c r="I8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K8" t="str">
-        <v>BS-003</v>
-      </c>
-      <c r="L8" t="str"/>
-      <c r="M8" t="str"/>
-      <c r="N8" t="str"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>BS-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Stage UI</v>
-      </c>
-      <c r="C9" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Build IntentCard, PlanCard, AgentActivityFeed</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Cards render from typed StageObjects and preserve visual thesis.</v>
-      </c>
-      <c r="I9" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K9" t="str">
-        <v>BS-004, BS-007</v>
-      </c>
-      <c r="L9" t="str"/>
-      <c r="M9" t="str"/>
-      <c r="N9" t="str"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>BS-009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Trust</v>
-      </c>
-      <c r="C10" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Build ApprovalCard and approval history</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Approval card shows action, scope, risk, consequence, undo path.</v>
-      </c>
-      <c r="I10" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K10" t="str">
-        <v>BS-003, BS-007</v>
-      </c>
-      <c r="L10" t="str"/>
-      <c r="M10" t="str"/>
-      <c r="N10" t="str"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>BS-010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Artifacts</v>
-      </c>
-      <c r="C11" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Build ArtifactCard and CodexTaskCard</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Approving creates artifact/Codex task cards.</v>
-      </c>
-      <c r="I11" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K11" t="str">
-        <v>BS-009</v>
-      </c>
-      <c r="L11" t="str"/>
-      <c r="M11" t="str"/>
-      <c r="N11" t="str"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>BS-011</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Research</v>
-      </c>
-      <c r="C12" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Implement local research event logger</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Key product events logged with session ids and timestamps.</v>
-      </c>
-      <c r="I12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K12" t="str">
-        <v>BS-003</v>
-      </c>
-      <c r="L12" t="str"/>
-      <c r="M12" t="str"/>
-      <c r="N12" t="str"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>BS-012</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Research</v>
-      </c>
-      <c r="C13" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Add session event export and research note generator</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H13" t="str">
-        <v>User can export JSON and create markdown note draft.</v>
-      </c>
-      <c r="I13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K13" t="str">
-        <v>BS-011</v>
-      </c>
-      <c r="L13" t="str"/>
-      <c r="M13" t="str"/>
-      <c r="N13" t="str"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>BS-013</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Stage UX</v>
-      </c>
-      <c r="C14" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Add demo fixtures: Build Blackstage, Acquisition Analysis, Research Synthesis</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Fixture selector runs each demo without private data.</v>
-      </c>
-      <c r="I14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K14" t="str">
-        <v>BS-007, BS-008</v>
-      </c>
-      <c r="L14" t="str"/>
-      <c r="M14" t="str"/>
-      <c r="N14" t="str"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>BS-014</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Voice</v>
-      </c>
-      <c r="C15" t="str">
-        <v>2 Conversation</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Add voice input experiment</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H15" t="str">
-        <v>User can submit spoken intent or use fallback text.</v>
-      </c>
-      <c r="I15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K15" t="str">
-        <v>BS-005</v>
-      </c>
-      <c r="L15" t="str"/>
-      <c r="M15" t="str"/>
-      <c r="N15" t="str"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>BS-015</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Artifacts</v>
-      </c>
-      <c r="C16" t="str">
-        <v>2 Conversation</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Implement markdown artifact export</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Artifacts export as markdown with provenance.</v>
-      </c>
-      <c r="I16" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K16" t="str">
-        <v>BS-010</v>
-      </c>
-      <c r="L16" t="str"/>
-      <c r="M16" t="str"/>
-      <c r="N16" t="str"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>BS-016</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Trust</v>
-      </c>
-      <c r="C17" t="str">
-        <v>3 Agent Runtime</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Implement approval policy engine</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H17" t="str">
-        <v>External/financial/credential/destructive actions always require approval.</v>
-      </c>
-      <c r="I17" t="s">
-        <v>85</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K17" t="str">
-        <v>BS-009</v>
-      </c>
-      <c r="L17" t="str"/>
-      <c r="M17" t="str"/>
-      <c r="N17" t="str"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>BS-017</v>
-      </c>
-      <c r="B18" t="str">
-        <v>AI Building</v>
-      </c>
-      <c r="C18" t="str">
-        <v>3 Agent Runtime</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Add Codex task export artifact</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Stage can generate Codex-ready task briefs from an intent thread.</v>
-      </c>
-      <c r="I18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K18" t="str">
-        <v>BS-010, BS-012</v>
-      </c>
-      <c r="L18" t="str"/>
-      <c r="M18" t="str"/>
-      <c r="N18" t="str"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>BS-018</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Quality</v>
-      </c>
-      <c r="C19" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Create visual QA screenshots for demo states</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Screenshots show idle, working, approval, artifact states.</v>
-      </c>
-      <c r="I19" t="s">
-        <v>101</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K19" t="str">
-        <v>BS-004, BS-008, BS-009</v>
-      </c>
-      <c r="L19" t="str"/>
-      <c r="M19" t="str"/>
-      <c r="N19" t="str"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" t="s">
-        <v>132</v>
-      </c>
-      <c r="J20" t="s">
-        <v>133</v>
-      </c>
-      <c r="K20" t="s">
-        <v>134</v>
-      </c>
-      <c r="L20" t="s">
-        <v>135</v>
-      </c>
-      <c r="M20" t="s">
-        <v>136</v>
-      </c>
-      <c r="N20" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>BS-020</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Stage Frontend</v>
-      </c>
-      <c r="C21" t="str">
-        <v>1 Stage Shell v0</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Browser compact render QA and orb voice entry</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Done</v>
-      </c>
-      <c r="F21" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Codex</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Browser in-app compact viewport keeps active stage regions separated and live voice/debug controls reachable.</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Browser plugin geometry check reports zero overlaps and visible Speak/Export controls.</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="K21" t="str">
-        <v>BS-018, BS-019</v>
-      </c>
-      <c r="L21" t="str"/>
-      <c r="M21" t="str"/>
-      <c r="N21" t="str">
-        <v>Logged in 2026-05-15 browser compact render slice.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BS-021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Stage Rendering</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1 Stage Shell v0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Make render field the goal center: semantic stage coordinates and focal floor</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Active field uses scene coordinates, a focal floor/horizon, hidden QA deep links, and Browser evidence without visible demo buttons.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Browser desktop/mobile visual QA; typecheck/lint/build/test</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>BS-019, BS-020</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Next: central approval ritual and geometric agent labor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BS-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Stage Rendering</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1 Stage Shell v0</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Turn approval and agent labor into central cinematic scene objects</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Pending approvals dim the field and become central ritual objects; agent labor can expand from geometry into audit feed.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Browser visual QA plus e2e scene-manifest assertions</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>BS-021</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Reference video frames show approval/action and labor geometry as the next gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BS-023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stage Rendering</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1 Stage Shell v0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Add semantic render zones and flow spine</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>StageSceneManifest emits active zones; StageSceneField renders zone bands/flow; approved desktop scenes keep objects and command dock clear.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Browser desktop geometry QA and targeted e2e overlap gate pass.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>BS-021, BS-022</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Browser found approved-scene overlap; anchors and zone grammar were retuned. Next: central approval ritual.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="E2:E19">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>E2="Done"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>E2="Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>F2="P0"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="E2:E19">
-      <formula1>"Not Started,In Progress,Blocked,Done,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F2:F19">
-      <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="J2:J19">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart ns1:id="R281c859479774d5c"/>
-  </tableParts>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="52" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Workstream</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Acceptance Criteria</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Verification</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>Research Log Required</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>PR Link</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>Due Date</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>BS-001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Foundation</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>0 Foundation</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Initialize monorepo and workspace commands</x:v>
+      </x:c>
+      <x:c r="E2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Repo has apps/packages structure and install/dev/build/typecheck commands.</x:v>
+      </x:c>
+      <x:c r="I2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K2" t="str"/>
+      <x:c r="L2" t="str"/>
+      <x:c r="M2" t="str"/>
+      <x:c r="N2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>BS-002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Foundation</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>0 Foundation</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Install AGENTS.md and docs into repo root</x:v>
+      </x:c>
+      <x:c r="E3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Cheick + Codex</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Codex can summarize project mission and active instructions.</x:v>
+      </x:c>
+      <x:c r="I3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>BS-001</x:v>
+      </x:c>
+      <x:c r="L3" t="str"/>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>BS-003</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Core State</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Define IntentThread, StageObject, AgentEvent, ApprovalRequest, Artifact, ResearchEvent types</x:v>
+      </x:c>
+      <x:c r="E4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Types exported from stage-core and used by app.</x:v>
+      </x:c>
+      <x:c r="I4" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>BS-001</x:v>
+      </x:c>
+      <x:c r="L4" t="str"/>
+      <x:c r="M4" t="str"/>
+      <x:c r="N4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>BS-004</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Stage Frontend</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Build full-screen black StageRoot and PresenceCore</x:v>
+      </x:c>
+      <x:c r="E5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>Idle stage looks cinematic and not like chatbot.</x:v>
+      </x:c>
+      <x:c r="I5" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>BS-001</x:v>
+      </x:c>
+      <x:c r="L5" t="str"/>
+      <x:c r="M5" t="str"/>
+      <x:c r="N5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>BS-005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Stage Frontend</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Add text intent submission and transcript display</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>User submits intent and sees it captured as first-class object.</x:v>
+      </x:c>
+      <x:c r="I6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>BS-003, BS-004</x:v>
+      </x:c>
+      <x:c r="L6" t="str"/>
+      <x:c r="M6" t="str"/>
+      <x:c r="N6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>BS-006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Core State</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Create intent thread reducer and local persistence</x:v>
+      </x:c>
+      <x:c r="E7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Threads persist across reload and can be resumed.</x:v>
+      </x:c>
+      <x:c r="I7" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>BS-003</x:v>
+      </x:c>
+      <x:c r="L7" t="str"/>
+      <x:c r="M7" t="str"/>
+      <x:c r="N7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>BS-007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Agent Runtime</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Implement simulated agent event stream</x:v>
+      </x:c>
+      <x:c r="E8" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Activity feed streams planned/started/progress/completed/approval_needed events.</x:v>
+      </x:c>
+      <x:c r="I8" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>BS-003</x:v>
+      </x:c>
+      <x:c r="L8" t="str"/>
+      <x:c r="M8" t="str"/>
+      <x:c r="N8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>BS-008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Stage UI</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Build IntentCard, PlanCard, AgentActivityFeed</x:v>
+      </x:c>
+      <x:c r="E9" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Cards render from typed StageObjects and preserve visual thesis.</x:v>
+      </x:c>
+      <x:c r="I9" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>BS-004, BS-007</x:v>
+      </x:c>
+      <x:c r="L9" t="str"/>
+      <x:c r="M9" t="str"/>
+      <x:c r="N9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>BS-009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Trust</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Build ApprovalCard and approval history</x:v>
+      </x:c>
+      <x:c r="E10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Approval card shows action, scope, risk, consequence, undo path.</x:v>
+      </x:c>
+      <x:c r="I10" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>BS-003, BS-007</x:v>
+      </x:c>
+      <x:c r="L10" t="str"/>
+      <x:c r="M10" t="str"/>
+      <x:c r="N10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>BS-010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Artifacts</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Build ArtifactCard and CodexTaskCard</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Approving creates artifact/Codex task cards.</x:v>
+      </x:c>
+      <x:c r="I11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>BS-009</x:v>
+      </x:c>
+      <x:c r="L11" t="str"/>
+      <x:c r="M11" t="str"/>
+      <x:c r="N11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>BS-011</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Research</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Implement local research event logger</x:v>
+      </x:c>
+      <x:c r="E12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Key product events logged with session ids and timestamps.</x:v>
+      </x:c>
+      <x:c r="I12" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>BS-003</x:v>
+      </x:c>
+      <x:c r="L12" t="str"/>
+      <x:c r="M12" t="str"/>
+      <x:c r="N12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>BS-012</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Research</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Add session event export and research note generator</x:v>
+      </x:c>
+      <x:c r="E13" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>User can export JSON and create markdown note draft.</x:v>
+      </x:c>
+      <x:c r="I13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>BS-011</x:v>
+      </x:c>
+      <x:c r="L13" t="str"/>
+      <x:c r="M13" t="str"/>
+      <x:c r="N13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>BS-013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Stage UX</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Add demo fixtures: Build Blackstage, Acquisition Analysis, Research Synthesis</x:v>
+      </x:c>
+      <x:c r="E14" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Fixture selector runs each demo without private data.</x:v>
+      </x:c>
+      <x:c r="I14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>BS-007, BS-008</x:v>
+      </x:c>
+      <x:c r="L14" t="str"/>
+      <x:c r="M14" t="str"/>
+      <x:c r="N14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>BS-014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Voice</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>2 Conversation</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Add voice input experiment</x:v>
+      </x:c>
+      <x:c r="E15" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>User can submit spoken intent or use fallback text.</x:v>
+      </x:c>
+      <x:c r="I15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>BS-005</x:v>
+      </x:c>
+      <x:c r="L15" t="str"/>
+      <x:c r="M15" t="str"/>
+      <x:c r="N15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>BS-015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Artifacts</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>2 Conversation</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Implement markdown artifact export</x:v>
+      </x:c>
+      <x:c r="E16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Artifacts export as markdown with provenance.</x:v>
+      </x:c>
+      <x:c r="I16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>BS-010</x:v>
+      </x:c>
+      <x:c r="L16" t="str"/>
+      <x:c r="M16" t="str"/>
+      <x:c r="N16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>BS-016</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Trust</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>3 Agent Runtime</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Implement approval policy engine</x:v>
+      </x:c>
+      <x:c r="E17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>External/financial/credential/destructive actions always require approval.</x:v>
+      </x:c>
+      <x:c r="I17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>BS-009</x:v>
+      </x:c>
+      <x:c r="L17" t="str"/>
+      <x:c r="M17" t="str"/>
+      <x:c r="N17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>BS-017</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>AI Building</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>3 Agent Runtime</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Add Codex task export artifact</x:v>
+      </x:c>
+      <x:c r="E18" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Stage can generate Codex-ready task briefs from an intent thread.</x:v>
+      </x:c>
+      <x:c r="I18" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>BS-010, BS-012</x:v>
+      </x:c>
+      <x:c r="L18" t="str"/>
+      <x:c r="M18" t="str"/>
+      <x:c r="N18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>BS-018</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Quality</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Create visual QA screenshots for demo states</x:v>
+      </x:c>
+      <x:c r="E19" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Screenshots show idle, working, approval, artifact states.</x:v>
+      </x:c>
+      <x:c r="I19" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>BS-004, BS-008, BS-009</x:v>
+      </x:c>
+      <x:c r="L19" t="str"/>
+      <x:c r="M19" t="str"/>
+      <x:c r="N19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E20" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F20" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G20" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H20" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="I20" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J20" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="K20" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="L20" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="M20" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="N20" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>BS-020</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Stage Frontend</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>1 Stage Shell v0</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Browser compact render QA and orb voice entry</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Browser in-app compact viewport keeps active stage regions separated and live voice/debug controls reachable.</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Browser plugin geometry check reports zero overlaps and visible Speak/Export controls.</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>BS-018, BS-019</x:v>
+      </x:c>
+      <x:c r="L21" t="str"/>
+      <x:c r="M21" t="str"/>
+      <x:c r="N21" t="str">
+        <x:v>Logged in 2026-05-15 browser compact render slice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="inlineStr">
+        <x:is>
+          <x:t>BS-021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" t="inlineStr">
+        <x:is>
+          <x:t>Stage Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" t="inlineStr">
+        <x:is>
+          <x:t>1 Stage Shell v0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" t="inlineStr">
+        <x:is>
+          <x:t>Make render field the goal center: semantic stage coordinates and focal floor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" t="inlineStr">
+        <x:is>
+          <x:t>Done</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" t="inlineStr">
+        <x:is>
+          <x:t>P0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" t="inlineStr">
+        <x:is>
+          <x:t>Active field uses scene coordinates, a focal floor/horizon, hidden QA deep links, and Browser evidence without visible demo buttons.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I22" t="inlineStr">
+        <x:is>
+          <x:t>Browser desktop/mobile visual QA; typecheck/lint/build/test</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J22" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K22" t="inlineStr">
+        <x:is>
+          <x:t>BS-019, BS-020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L22" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="M22" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N22" t="inlineStr">
+        <x:is>
+          <x:t>Next: central approval ritual and geometric agent labor.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="inlineStr">
+        <x:is>
+          <x:t>BS-022</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" t="inlineStr">
+        <x:is>
+          <x:t>Stage Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" t="inlineStr">
+        <x:is>
+          <x:t>1 Stage Shell v0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" t="inlineStr">
+        <x:is>
+          <x:t>Turn approval and agent labor into central cinematic scene objects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" t="inlineStr">
+        <x:is>
+          <x:t>Planned</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" t="inlineStr">
+        <x:is>
+          <x:t>P0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" t="inlineStr">
+        <x:is>
+          <x:t>Pending approvals dim the field and become central ritual objects; agent labor can expand from geometry into audit feed.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I23" t="inlineStr">
+        <x:is>
+          <x:t>Browser visual QA plus e2e scene-manifest assertions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J23" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K23" t="inlineStr">
+        <x:is>
+          <x:t>BS-021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="M23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="N23" t="inlineStr">
+        <x:is>
+          <x:t>Reference video frames show approval/action and labor geometry as the next gap.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="inlineStr">
+        <x:is>
+          <x:t>BS-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" t="inlineStr">
+        <x:is>
+          <x:t>Stage Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" t="inlineStr">
+        <x:is>
+          <x:t>1 Stage Shell v0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" t="inlineStr">
+        <x:is>
+          <x:t>Add semantic render zones and flow spine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" t="inlineStr">
+        <x:is>
+          <x:t>Done</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" t="inlineStr">
+        <x:is>
+          <x:t>P0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" t="inlineStr">
+        <x:is>
+          <x:t>StageSceneManifest emits active zones; StageSceneField renders zone bands/flow; approved desktop scenes keep objects and command dock clear.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I24" t="inlineStr">
+        <x:is>
+          <x:t>Browser desktop geometry QA and targeted e2e overlap gate pass.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J24" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K24" t="inlineStr">
+        <x:is>
+          <x:t>BS-021, BS-022</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L24" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="M24" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N24" t="inlineStr">
+        <x:is>
+          <x:t>Browser found approved-scene overlap; anchors and zone grammar were retuned. Next: central approval ritual.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="inlineStr">
+        <x:is>
+          <x:t>BS-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" t="inlineStr">
+        <x:is>
+          <x:t>Stage Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" t="inlineStr">
+        <x:is>
+          <x:t>1 Stage Shell v0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" t="inlineStr">
+        <x:is>
+          <x:t>Add central approval threshold and labor orbit field</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" t="inlineStr">
+        <x:is>
+          <x:t>Done</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" t="inlineStr">
+        <x:is>
+          <x:t>P0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" t="inlineStr">
+        <x:is>
+          <x:t>Pending approvals render as central field thresholds; recent agent events render as visible labor nodes; right rail remains the single explicit approval control surface.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" t="inlineStr">
+        <x:is>
+          <x:t>Browser plugin QA plus e2e confirm one approve button, threshold visible, labor nodes visible, and no plan/command/threshold overlap.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J25" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K25" t="inlineStr">
+        <x:is>
+          <x:t>BS-022, BS-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L25" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="M25" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N25" t="inlineStr">
+        <x:is>
+          <x:t>Rendering-first slice toward central ritual field and geometric labor.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="E2:E19">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>E2="Done"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>E2="Blocked"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F2:F19">
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>F2="P0"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="E2:E19">
+      <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F19">
+      <x:formula1>"P0,P1,P2,P3"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J19">
+      <x:formula1>"Yes,No"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="R281c859479774d5c"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2975,921 +3047,1040 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="32" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="36" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="36" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="36" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="36" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="36" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="6" t="str">
-        <v>Log ID</v>
-      </c>
-      <c r="B1" s="6" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" s="6" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" s="6" t="str">
-        <v>Related Task/Experiment</v>
-      </c>
-      <c r="E1" s="6" t="str">
-        <v>Prompt/Scenario</v>
-      </c>
-      <c r="F1" s="6" t="str">
-        <v>What Worked</v>
-      </c>
-      <c r="G1" s="6" t="str">
-        <v>What Failed</v>
-      </c>
-      <c r="H1" s="6" t="str">
-        <v>Human Interventions</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <v>Product Insight</v>
-      </c>
-      <c r="J1" s="6" t="str">
-        <v>AI-Building Insight</v>
-      </c>
-      <c r="K1" s="6" t="str">
-        <v>Evidence Link</v>
-      </c>
-      <c r="L1" s="6" t="str">
-        <v>Next Action</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>LOG-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Build</v>
-      </c>
-      <c r="D2" t="str">
-        <v>BS-001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Bootstrap repo</v>
-      </c>
-      <c r="F2" t="str"/>
-      <c r="G2" t="str"/>
-      <c r="H2" t="str"/>
-      <c r="I2" t="str"/>
-      <c r="J2" t="str"/>
-      <c r="K2" t="str"/>
-      <c r="L2" t="str"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K6" t="s">
-        <v>148</v>
-      </c>
-      <c r="L6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LOG-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C7" t="str">
-        <v>UX/Validation</v>
-      </c>
-      <c r="D7" t="str">
-        <v>BS-020</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Browser compact render and orb entry QA</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Idle orb is demo-free; compact active field keeps intent, plan, evidence, labor, approval, artifact, command, and research zones separated.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Initial compact pass hid command/debug; focused dock then overlapped the document object before the one-row compact fix.</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Cheick explicitly corrected tool choice to Browser plugin.</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Quiet chrome must stay reachable; hidden controls cannot block live testing.</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Browser plugin catches real in-app viewport issues that headless gates can miss.</v>
-      </c>
-      <c r="K7" t="str">
-        <v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Continue StageSceneField vector layer and live voice debug QA.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LOG-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>UX/Research</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BS-021</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Frame-by-frame render field reference analysis</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Extracted all 192 frames and translated the video into stage, focal, approval, and labor requirements.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Confirmed prior UI still leaned too much toward cards/dashboard composition.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Cheick supplied a second cinematic reference and redirected the goal toward rendering field animation.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>One focal object plus orbiting support reads smarter than many equal panels.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Frame sampling turned taste feedback into concrete renderer requirements.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>docs/research/runs/2026-05-15-render-field-reference-analysis.md</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Build central approval ritual and geometric labor field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LOG-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>UX/Build</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BS-021</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Semantic stage-coordinate render pass</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>StageSceneManifest now drives x/y/depth/scale; StageSceneField draws focal floor and horizon; Browser QA shows no active-field overlaps.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Browser input path exposed clipboard limitations, so hidden scenario/instant QA links were added.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None beyond Cheick's rendering-first correction.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>The field must own organization; CSS grid placement is not enough.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Browser visual checks need deterministic deep links that do not pollute startup UX.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>docs/research/runs/2026-05-15-stage-scene-field-vector-slice.md</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Make approval and labor materialize as central scene states.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LOG-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>UX/Build</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BS-023</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Render zone flow and overlap hardening</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Added semantic scene zones, zone-flow spine, retuned anchors, and e2e geometry checks for approved scenes.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Browser desktop QA exposed focal-plan overlap from secondary task/model objects before the retune.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Cheick asked to continue systematically toward the reality-interface goal.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>The field needs a visible grammar, not only better object coordinates.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Browser geometry turns taste feedback into deterministic renderer work.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Make approval and visible labor feel central instead of rail-shaped.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C100">
-      <formula1>"Build,Product,User Study,Experiment,Decision,Failure"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart ns1:id="Rdb356ef7547d4528"/>
-  </tableParts>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="36" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Log ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Related Task/Experiment</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Prompt/Scenario</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>What Worked</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>What Failed</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Human Interventions</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Product Insight</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>AI-Building Insight</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>Evidence Link</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>Next Action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>LOG-001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>2026-05-10</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Build</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>BS-001</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Bootstrap repo</x:v>
+      </x:c>
+      <x:c r="F2" t="str"/>
+      <x:c r="G2" t="str"/>
+      <x:c r="H2" t="str"/>
+      <x:c r="I2" t="str"/>
+      <x:c r="J2" t="str"/>
+      <x:c r="K2" t="str"/>
+      <x:c r="L2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I4" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J4" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E5" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F5" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G5" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H5" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I5" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="J5" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B6" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D6" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F6" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="I6" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J6" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="L6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>LOG-006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>UX/Validation</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>BS-020</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Browser compact render and orb entry QA</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Idle orb is demo-free; compact active field keeps intent, plan, evidence, labor, approval, artifact, command, and research zones separated.</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Initial compact pass hid command/debug; focused dock then overlapped the document object before the one-row compact fix.</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Cheick explicitly corrected tool choice to Browser plugin.</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Quiet chrome must stay reachable; hidden controls cannot block live testing.</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Browser plugin catches real in-app viewport issues that headless gates can miss.</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>Continue StageSceneField vector layer and live voice debug QA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t>LOG-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>UX/Research</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t>BS-021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" t="inlineStr">
+        <x:is>
+          <x:t>Frame-by-frame render field reference analysis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" t="inlineStr">
+        <x:is>
+          <x:t>Extracted all 192 frames and translated the video into stage, focal, approval, and labor requirements.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" t="inlineStr">
+        <x:is>
+          <x:t>Confirmed prior UI still leaned too much toward cards/dashboard composition.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" t="inlineStr">
+        <x:is>
+          <x:t>Cheick supplied a second cinematic reference and redirected the goal toward rendering field animation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" t="inlineStr">
+        <x:is>
+          <x:t>One focal object plus orbiting support reads smarter than many equal panels.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" t="inlineStr">
+        <x:is>
+          <x:t>Frame sampling turned taste feedback into concrete renderer requirements.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-15-render-field-reference-analysis.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" t="inlineStr">
+        <x:is>
+          <x:t>Build central approval ritual and geometric labor field.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>LOG-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>UX/Build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t>BS-021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" t="inlineStr">
+        <x:is>
+          <x:t>Semantic stage-coordinate render pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t>StageSceneManifest now drives x/y/depth/scale; StageSceneField draws focal floor and horizon; Browser QA shows no active-field overlaps.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" t="inlineStr">
+        <x:is>
+          <x:t>Browser input path exposed clipboard limitations, so hidden scenario/instant QA links were added.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" t="inlineStr">
+        <x:is>
+          <x:t>None beyond Cheick's rendering-first correction.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" t="inlineStr">
+        <x:is>
+          <x:t>The field must own organization; CSS grid placement is not enough.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>Browser visual checks need deterministic deep links that do not pollute startup UX.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-15-stage-scene-field-vector-slice.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" t="inlineStr">
+        <x:is>
+          <x:t>Make approval and labor materialize as central scene states.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>LOG-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>UX/Build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t>BS-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" t="inlineStr">
+        <x:is>
+          <x:t>Render zone flow and overlap hardening</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t>Added semantic scene zones, zone-flow spine, retuned anchors, and e2e geometry checks for approved scenes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" t="inlineStr">
+        <x:is>
+          <x:t>Browser desktop QA exposed focal-plan overlap from secondary task/model objects before the retune.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" t="inlineStr">
+        <x:is>
+          <x:t>Cheick asked to continue systematically toward the reality-interface goal.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" t="inlineStr">
+        <x:is>
+          <x:t>The field needs a visible grammar, not only better object coordinates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t>Browser geometry turns taste feedback into deterministic renderer work.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L10" t="inlineStr">
+        <x:is>
+          <x:t>Make approval and visible labor feel central instead of rail-shaped.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>LOG-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>UX/Build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t>BS-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Approval ritual and labor field slice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>Central StageRitualField made approvals and recent agent work visible in the render field without duplicating approval controls.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t>The threshold is still a compact symbolic object; next pass should make the relevant work object itself become the approval instrument.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t>Cheick redirected the goal toward rendering-field quality and away from backend-only progress.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="inlineStr">
+        <x:is>
+          <x:t>Approval and labor need to be spatial field events, not only sidebar/audit rows.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" t="inlineStr">
+        <x:is>
+          <x:t>Browser geometry checks turned the cinematic critique into measurable overlap and control-count gates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-16-approval-ritual-labor-field-slice.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" t="inlineStr">
+        <x:is>
+          <x:t>Evolve the symbolic threshold into a field-dimming approval ritual tied to the specific object/action.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="C2:C100">
+      <x:formula1>"Build,Product,User Study,Experiment,Decision,Failure"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="Rdb356ef7547d4528"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="38" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="26" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="30" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="6" t="str">
-        <v>Decision ID</v>
-      </c>
-      <c r="B1" s="6" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" s="6" t="str">
-        <v>Area</v>
-      </c>
-      <c r="D1" s="6" t="str">
-        <v>Decision</v>
-      </c>
-      <c r="E1" s="6" t="str">
-        <v>Status</v>
-      </c>
-      <c r="F1" s="6" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G1" s="6" t="str">
-        <v>Rationale</v>
-      </c>
-      <c r="H1" s="6" t="str">
-        <v>Options Considered</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <v>Evidence Link</v>
-      </c>
-      <c r="J1" s="6" t="str">
-        <v>Review Date</v>
-      </c>
-      <c r="K1" s="6" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DEC-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Product</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Start with Stage Shell v0 before full OS replacement.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Cheick</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Prove the living render field before broad integrations.</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Full OS; browser prototype; design-only mock</v>
-      </c>
-      <c r="I2" t="str">
-        <v>docs/06_mvp_stage_shell_spec.md</v>
-      </c>
-      <c r="J2" t="str"/>
-      <c r="K2" t="str"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>DEC-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Research</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Instrument product and build process from day one.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Cheick + GPT-5.5 Pro</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Research output is part of the mission.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Add later; manual notes; instrument now</v>
-      </c>
-      <c r="I3" t="str">
-        <v>docs/14_research_protocol.md</v>
-      </c>
-      <c r="J3" t="str"/>
-      <c r="K3" t="str"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" t="s">
-        <v>113</v>
-      </c>
-      <c r="I6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H7" t="s">
-        <v>157</v>
-      </c>
-      <c r="I7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>DEC-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Rendering</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Compact active sessions must keep voice and debug entrypoints reachable instead of hiding them completely.</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Cheick + Codex</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Live testing depends on visible Speak and debug export controls even when the field is intentionally quiet.</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Hide all chrome; always show full panels; compact one-row command and trace controls</v>
-      </c>
-      <c r="I8" t="str">
-        <v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Browser plugin geometry check is the acceptance gate for compact active sessions.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DEC-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Rendering</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>The active goal is rendering-first until the field itself feels like organized intelligence.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cheick + Codex</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>The project thesis fails if runtime features work but the surface still reads like a dark dashboard.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Continue backend/runtime first; polish cards; render-field-first goal amendment.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>codex/goals/first_long_run_stage_shell_v0_after_prompt1.md</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Reference video 2 is now a north-star artifact for stage composition and motion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DEC-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Use hidden deep-link QA parameters for visual scenarios instead of visible demo buttons.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>The startup UX must remain one orb and one instruction while Browser QA still needs deterministic active states.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Visible demo buttons; manual typing only; hidden query controls.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>docs/28_cinematic_rendering_system.md</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Supported query controls: stageScenario, stageIntent, stageInstant, stageDelayMultiplier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DEC-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rendering</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Render organization belongs in semantic zones plus measured geometry gates, not only CSS placement.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>The user must feel the field organizing intelligence before reading individual cards.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Card coordinates only; semantic zones; full physics engine.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>The next renderer target is central approval and labor geometry.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="C2:C100">
-      <formula1>"Product,UX,Architecture,Research,Security,Business"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E2:E100">
-      <formula1>"Proposed,Accepted,Rejected,Superseded"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart ns1:id="Rb9393f6f1d2545c7"/>
-  </tableParts>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Decision ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Rationale</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Options Considered</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Evidence Link</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>Review Date</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>DEC-001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>2026-05-10</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Start with Stage Shell v0 before full OS replacement.</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Accepted</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Cheick</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Prove the living render field before broad integrations.</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Full OS; browser prototype; design-only mock</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>docs/06_mvp_stage_shell_spec.md</x:v>
+      </x:c>
+      <x:c r="J2" t="str"/>
+      <x:c r="K2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>DEC-002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>2026-05-10</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Research</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Instrument product and build process from day one.</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Accepted</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Cheick + GPT-5.5 Pro</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Research output is part of the mission.</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Add later; manual notes; instrument now</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>docs/14_research_protocol.md</x:v>
+      </x:c>
+      <x:c r="J3" t="str"/>
+      <x:c r="K3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I4" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F5" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B6" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D6" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H6" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I6" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="J6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B7" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E7" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F7" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G7" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H7" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="I7" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J7" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="K7" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>DEC-007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Rendering</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Compact active sessions must keep voice and debug entrypoints reachable instead of hiding them completely.</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Accepted</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Cheick + Codex</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>Live testing depends on visible Speak and debug export controls even when the field is intentionally quiet.</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Hide all chrome; always show full panels; compact one-row command and trace controls</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>docs/research/runs/2026-05-15-browser-compact-render-and-orb-entry-slice.md</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>2026-05-22</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Browser plugin geometry check is the acceptance gate for compact active sessions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>DEC-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t>The active goal is rendering-first until the field itself feels like organized intelligence.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" t="inlineStr">
+        <x:is>
+          <x:t>Accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t>Cheick + Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" t="inlineStr">
+        <x:is>
+          <x:t>The project thesis fails if runtime features work but the surface still reads like a dark dashboard.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" t="inlineStr">
+        <x:is>
+          <x:t>Continue backend/runtime first; polish cards; render-field-first goal amendment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" t="inlineStr">
+        <x:is>
+          <x:t>codex/goals/first_long_run_stage_shell_v0_after_prompt1.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" t="inlineStr">
+        <x:is>
+          <x:t>Reference video 2 is now a north-star artifact for stage composition and motion.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>DEC-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>Validation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t>Use hidden deep-link QA parameters for visual scenarios instead of visible demo buttons.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" t="inlineStr">
+        <x:is>
+          <x:t>Accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" t="inlineStr">
+        <x:is>
+          <x:t>The startup UX must remain one orb and one instruction while Browser QA still needs deterministic active states.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" t="inlineStr">
+        <x:is>
+          <x:t>Visible demo buttons; manual typing only; hidden query controls.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" t="inlineStr">
+        <x:is>
+          <x:t>docs/28_cinematic_rendering_system.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" t="inlineStr">
+        <x:is>
+          <x:t>Supported query controls: stageScenario, stageIntent, stageInstant, stageDelayMultiplier.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>DEC-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t>Render organization belongs in semantic zones plus measured geometry gates, not only CSS placement.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t>The user must feel the field organizing intelligence before reading individual cards.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t>Card coordinates only; semantic zones; full physics engine.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-16-render-zone-flow-slice.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" t="inlineStr">
+        <x:is>
+          <x:t>The next renderer target is central approval and labor geometry.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>DEC-011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t>Central approval/labor rendering is visual intelligence only; the right rail remains the explicit control and audit surface.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr">
+        <x:is>
+          <x:t>Accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" t="inlineStr">
+        <x:is>
+          <x:t>This gives the field the needed ritual feeling without creating duplicate approve buttons or ambiguous high-impact actions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" t="inlineStr">
+        <x:is>
+          <x:t>Move buttons into the field; leave approval only in rail; duplicate controls in both places.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" t="inlineStr">
+        <x:is>
+          <x:t>docs/28_cinematic_rendering_system.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" t="inlineStr">
+        <x:is>
+          <x:t>Revisit when the approval object becomes more immersive.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="C2:C100">
+      <x:formula1>"Product,UX,Architecture,Research,Security,Business"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E2:E100">
+      <x:formula1>"Proposed,Accepted,Rejected,Superseded"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="Rb9393f6f1d2545c7"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>

--- a/BlackStage_OS_Development_Tracker.xlsx
+++ b/BlackStage_OS_Development_Tracker.xlsx
@@ -846,7 +846,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N25" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BacklogTable" displayName="BacklogTable" ref="A1:N26" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Workstream"/>
@@ -2786,6 +2786,78 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="inlineStr">
+        <x:is>
+          <x:t>BS-025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" t="inlineStr">
+        <x:is>
+          <x:t>Stage Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" t="inlineStr">
+        <x:is>
+          <x:t>1 Stage Shell v0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" t="inlineStr">
+        <x:is>
+          <x:t>Bind pending approval to focused work object</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" t="inlineStr">
+        <x:is>
+          <x:t>Done</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" t="inlineStr">
+        <x:is>
+          <x:t>P0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" t="inlineStr">
+        <x:is>
+          <x:t>Pending approval derives one focus object, dims surrounding objects, and draws a visible tether from object to approval threshold.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I26" t="inlineStr">
+        <x:is>
+          <x:t>Browser plugin QA plus e2e confirm one focus object, dimmed non-focus opacity, tether presence, and no threshold overlap.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J26" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K26" t="inlineStr">
+        <x:is>
+          <x:t>BS-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L26" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="M26" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N26" t="inlineStr">
+        <x:is>
+          <x:t>Makes approval feel like a field/camera event instead of a detached badge.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="E2:E19">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -3546,6 +3618,68 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>LOG-011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>UX/Build</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t>BS-025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr">
+        <x:is>
+          <x:t>Approval focus pull slice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" t="inlineStr">
+        <x:is>
+          <x:t>Pending approval now focuses the plan object, dims surrounding objects, and draws an approval tether in the field.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" t="inlineStr">
+        <x:is>
+          <x:t>Browser QA caught that animation was overriding dim opacity until the CSS state was hardened and e2e asserted computed opacity.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" t="inlineStr">
+        <x:is>
+          <x:t>Cheick kept the goal centered on rendering-field quality rather than accepting backend progress alone.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" t="inlineStr">
+        <x:is>
+          <x:t>Approval reads better when it behaves like a camera/focus event tied to the object under review.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" t="inlineStr">
+        <x:is>
+          <x:t>Computed-style Browser checks can catch visual cascade bugs that plain DOM presence checks miss.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" t="inlineStr">
+        <x:is>
+          <x:t>docs/research/runs/2026-05-16-approval-focus-pull-slice.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" t="inlineStr">
+        <x:is>
+          <x:t>Animate a stronger camera focus pull around the approval-bound object.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="C2:C100">
@@ -4064,6 +4198,63 @@
       <x:c r="K12" t="inlineStr">
         <x:is>
           <x:t>Revisit when the approval object becomes more immersive.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="inlineStr">
+        <x:is>
+          <x:t>DEC-012</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" t="inlineStr">
+        <x:is>
+          <x:t>Rendering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t>Pending approval should derive a single object-bound focus state from replayable thread and scene state.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" t="inlineStr">
+        <x:is>
+          <x:t>Accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" t="inlineStr">
+        <x:is>
+          <x:t>Codex</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" t="inlineStr">
+        <x:is>
+          <x:t>The field should show exactly what object/action is under review without storing separate visual-only approval state.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" t="inlineStr">
+        <x:is>
+          <x:t>Detached threshold only; duplicate approval controls in the field; store manual focus state.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" t="inlineStr">
+        <x:is>
+          <x:t>docs/05_system_architecture.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J13" t="inlineStr">
+        <x:is>
+          <x:t>2026-05-20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K13" t="inlineStr">
+        <x:is>
+          <x:t>Next review should evaluate whether the focus pull feels cinematic enough.</x:t>
         </x:is>
       </x:c>
     </x:row>
